--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_desert_bighorn_ram.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_desert_bighorn_ram.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="780" yWindow="135" windowWidth="25170" windowHeight="15345" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="2026_desert_bighorn_ram" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,14 +12,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026_desert_bighorn_ram'!$A$1:$O$26</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'2026_desert_bighorn_ram'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,12 +28,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="002B1C12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
@@ -47,8 +49,13 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -57,7 +64,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009A4E00"/>
+        <fgColor rgb="FF4F2D1D"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,8 +72,23 @@
         <fgColor rgb="004F2D1D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B301B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F1E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFE5D7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -75,119 +97,615 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thick">
+        <color rgb="FF2D1900"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF2D1900"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF2D1900"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF2D1900"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="00D8B58E"/>
+        <color rgb="00C58F61"/>
       </left>
       <right style="thin">
-        <color rgb="00D8B58E"/>
+        <color rgb="00C58F61"/>
       </right>
       <top style="thin">
-        <color rgb="00D8B58E"/>
+        <color rgb="00C58F61"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D8B58E"/>
+        <color rgb="00C58F61"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="general" vertical="center"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="general" vertical="center"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="general" vertical="center"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="general" vertical="center"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="general" vertical="center"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="general" vertical="center"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="general" vertical="center"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="general" vertical="center"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="general" vertical="center"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="general" vertical="center"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="general" vertical="center"/>
+      <border>
+        <left/>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top style="thick">
+          <color rgb="FF2D1900"/>
+        </top>
+        <bottom style="thick">
+          <color rgb="FF2D1900"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color auto="1"/>
+        <extend val="0"/>
+        <sz val="10"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color rgb="FFFFFFFF"/>
+        <extend val="0"/>
+        <sz val="11"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF4F2D1D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thick">
+          <color rgb="FF2D1900"/>
+        </left>
+        <right style="thick">
+          <color rgb="FF2D1900"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thick">
+          <color rgb="FF2D1900"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -205,11 +723,11 @@
     <tableColumn id="8" name="permits_2026_res"/>
     <tableColumn id="9" name="permits_2026_nr"/>
     <tableColumn id="10" name="permits_2026_total"/>
-    <tableColumn id="11" name="NOTES"/>
-    <tableColumn id="12" name="Harvest Prior Year"/>
-    <tableColumn id="13" name="Percent Harvest Success (previous hunting season)"/>
-    <tableColumn id="14" name="Average Age Harvested (previous hunting season)"/>
-    <tableColumn id="15" name="Avg Days Hunted (previous hunting season)"/>
+    <tableColumn id="11" name="Harvest Prior Year"/>
+    <tableColumn id="12" name="Percent Harvest Success"/>
+    <tableColumn id="13" name="Average Age Harvested"/>
+    <tableColumn id="14" name="Avg Days Hunted"/>
+    <tableColumn id="15" name="NOTES"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -507,1780 +1025,1778 @@
   <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="36" customWidth="1" min="13" max="13"/>
-    <col width="36" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="24" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="10" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="14" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="14" bestFit="1" customWidth="1" min="5" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" style="1" min="11" max="11"/>
+    <col width="20" customWidth="1" style="1" min="12" max="12"/>
+    <col width="20" customWidth="1" style="1" min="13" max="13"/>
+    <col width="14" customWidth="1" style="1" min="14" max="14"/>
+    <col width="10" bestFit="1" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>hunt_name</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>hunt_code</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>sex_type</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>species</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>hunt_type</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>permits_2026_res</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>permits_2026_nr</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>permits_2026_total</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
+        <is>
+          <t>Harvest Prior Year</t>
+        </is>
+      </c>
+      <c r="L1" s="16" t="inlineStr">
+        <is>
+          <t>Percent Harvest Success</t>
+        </is>
+      </c>
+      <c r="M1" s="16" t="inlineStr">
+        <is>
+          <t>Average Age Harvested</t>
+        </is>
+      </c>
+      <c r="N1" s="16" t="inlineStr">
+        <is>
+          <t>Avg Days Hunted</t>
+        </is>
+      </c>
+      <c r="O1" s="16" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Harvest Prior Year</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Percent Harvest Success (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Avg Days Hunted (previous hunting season)</t>
-        </is>
-      </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep - Statewide Permit</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>DS1000</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="21" t="inlineStr">
         <is>
           <t>Statewide</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="21" t="inlineStr">
         <is>
           <t>Sept 1 - Dec 31, 2026</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" s="6" t="inlineStr"/>
-      <c r="L2" s="7" t="n">
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" s="21" t="n">
         <v>2025</v>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="L2" s="22" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr"/>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="M2" s="22" t="n"/>
+      <c r="N2" s="22" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
+      <c r="O2" s="21" t="n"/>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Kaiparowits, East</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>DS1002</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="23" t="inlineStr">
         <is>
           <t>Sept 13, 2025 - Dec 31, 2025</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr"/>
-      <c r="L3" s="7" t="n">
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" s="23" t="n">
         <v>2025</v>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="L3" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
-      <c r="O3" s="7" t="inlineStr">
+      <c r="M3" s="24" t="n"/>
+      <c r="N3" s="24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
+      <c r="O3" s="23" t="n"/>
     </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Kaiparowits, Escalante East/West</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>DS1003</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t>Sept 12 - Nov 10, 2026</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr"/>
-      <c r="L4" s="7" t="n">
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="n">
         <v>2025</v>
       </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="L4" s="22" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr"/>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="M4" s="22" t="n"/>
+      <c r="N4" s="22" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
+      <c r="O4" s="21" t="n"/>
     </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>San Rafael, Dirty Devil</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>DS1004</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>Sept 13 - Dec 31, 2025</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr"/>
-      <c r="L5" s="7" t="n">
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="n">
         <v>2025</v>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="L5" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr"/>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
+      <c r="O5" s="23" t="n"/>
     </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Kaiparowits, West</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>DS1006</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>Sept 13, 2025 - Dec 31, 2025</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr"/>
-      <c r="L6" s="7" t="n">
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="n">
         <v>2025</v>
       </c>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="L6" s="22" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr"/>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="M6" s="22" t="n"/>
+      <c r="N6" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
+      <c r="O6" s="21" t="n"/>
     </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>San Rafael, South</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>DS1007</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>Sept 13, 2025 - Dec 31, 2025</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr"/>
-      <c r="L7" s="7" t="n">
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="n">
         <v>2025</v>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="L7" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr"/>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="M7" s="24" t="n"/>
+      <c r="N7" s="24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
+      <c r="O7" s="23" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Henry Mtns</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>DS6600</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr"/>
-      <c r="L8" s="7" t="n">
+      <c r="K8" s="21" t="n">
         <v>2025</v>
       </c>
-      <c r="M8" s="7" t="inlineStr">
+      <c r="L8" s="22" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr"/>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="M8" s="22" t="n"/>
+      <c r="N8" s="22" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
+      <c r="O8" s="21" t="n"/>
     </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Kaiparowits, East</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>DS6601</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="J9" s="24" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr"/>
-      <c r="L9" s="7" t="n">
+      <c r="K9" s="23" t="n">
         <v>2025</v>
       </c>
-      <c r="M9" s="7" t="inlineStr">
+      <c r="L9" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="M9" s="24" t="n"/>
+      <c r="N9" s="24" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
+      <c r="O9" s="23" t="n"/>
     </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Kaiparowits, West</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>DS6603</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr"/>
-      <c r="L10" s="7" t="n">
+      <c r="K10" s="21" t="n">
         <v>2025</v>
       </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr"/>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="22" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
+      <c r="O10" s="21" t="n"/>
     </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>La Sal, Potash/South Cisco</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>DS6604</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr"/>
-      <c r="L11" s="7" t="n">
+      <c r="K11" s="23" t="n">
         <v>2025</v>
       </c>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="L11" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr"/>
-      <c r="O11" s="7" t="inlineStr">
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="24" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
       </c>
+      <c r="O11" s="23" t="n"/>
     </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Pine Valley, Beaver Dam</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>DS6605</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>Sept 13, 2025 - Dec 31, 2025</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr"/>
-      <c r="L12" s="7" t="n">
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="n">
         <v>2025</v>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="L12" s="22" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr"/>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="M12" s="22" t="n"/>
+      <c r="N12" s="22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
+      <c r="O12" s="21" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>San Juan, Lockhart</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>DS6606</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr"/>
-      <c r="L13" s="7" t="n">
+      <c r="K13" s="23" t="n">
         <v>2025</v>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="L13" s="24" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr"/>
-      <c r="O13" s="7" t="inlineStr">
+      <c r="M13" s="24" t="n"/>
+      <c r="N13" s="24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
+      <c r="O13" s="23" t="n"/>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>San Juan, South</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>DS6607</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr"/>
-      <c r="L14" s="7" t="n">
+      <c r="K14" s="21" t="n">
         <v>2025</v>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="L14" s="22" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr"/>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="M14" s="22" t="n"/>
+      <c r="N14" s="22" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
+      <c r="O14" s="21" t="n"/>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>San Rafael, Dirty Devil</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>DS6608</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="J15" s="24" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr"/>
-      <c r="L15" s="7" t="n">
+      <c r="K15" s="23" t="n">
         <v>2025</v>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="L15" s="24" t="inlineStr">
         <is>
           <t>85.7</t>
         </is>
       </c>
-      <c r="N15" s="7" t="inlineStr"/>
-      <c r="O15" s="7" t="inlineStr">
+      <c r="M15" s="24" t="n"/>
+      <c r="N15" s="24" t="inlineStr">
         <is>
           <t>11.1</t>
         </is>
       </c>
+      <c r="O15" s="23" t="n"/>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>San Rafael, North</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>DS6609</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr"/>
-      <c r="L16" s="7" t="n">
+      <c r="K16" s="21" t="n">
         <v>2025</v>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="L16" s="22" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr"/>
-      <c r="O16" s="7" t="inlineStr">
+      <c r="M16" s="22" t="n"/>
+      <c r="N16" s="22" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
+      <c r="O16" s="21" t="n"/>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>San Rafael, South</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>DS6610</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="J17" s="24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr"/>
-      <c r="L17" s="7" t="n">
+      <c r="K17" s="23" t="n">
         <v>2025</v>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="L17" s="24" t="inlineStr">
         <is>
           <t>91.7</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr"/>
-      <c r="O17" s="7" t="inlineStr">
+      <c r="M17" s="24" t="n"/>
+      <c r="N17" s="24" t="inlineStr">
         <is>
           <t>11.2</t>
         </is>
       </c>
+      <c r="O17" s="23" t="n"/>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>Zion</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>DS6611</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K18" s="6" t="inlineStr"/>
-      <c r="L18" s="7" t="n">
+      <c r="K18" s="21" t="n">
         <v>2025</v>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="L18" s="22" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N18" s="7" t="inlineStr"/>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
+      <c r="M18" s="22" t="n"/>
+      <c r="N18" s="22" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="O18" s="21" t="n"/>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>Pine Valley, Virgin River</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>DS6620</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>Oct 24 2026 - Dec 25 2026</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr"/>
-      <c r="L19" s="7" t="n">
+      <c r="K19" s="23" t="n">
         <v>2025</v>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="L19" s="24" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr"/>
-      <c r="O19" s="7" t="inlineStr">
+      <c r="M19" s="24" t="n"/>
+      <c r="N19" s="24" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
+      <c r="O19" s="23" t="n"/>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>Pine Valley, Beaver Dam</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>DS6621</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>Oct 24 2026 - Dec 25 2026</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K20" s="6" t="inlineStr"/>
-      <c r="L20" s="7" t="n">
+      <c r="K20" s="21" t="n">
         <v>2025</v>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="L20" s="22" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr"/>
-      <c r="O20" s="7" t="inlineStr">
+      <c r="M20" s="22" t="n"/>
+      <c r="N20" s="22" t="inlineStr">
         <is>
           <t>11.7</t>
         </is>
       </c>
+      <c r="O20" s="21" t="n"/>
     </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>San Juan, North</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>DS6622</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" s="24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" s="24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K21" s="6" t="inlineStr"/>
-      <c r="L21" s="7" t="n">
+      <c r="K21" s="23" t="n">
         <v>2025</v>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="L21" s="24" t="inlineStr">
         <is>
           <t>33.3</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr"/>
-      <c r="O21" s="7" t="inlineStr">
+      <c r="M21" s="24" t="n"/>
+      <c r="N21" s="24" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
+      <c r="O21" s="23" t="n"/>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>San Juan, San Juan River</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>DS6623</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr"/>
-      <c r="L22" s="7" t="n">
+      <c r="K22" s="21" t="n">
         <v>2025</v>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="L22" s="22" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr"/>
-      <c r="O22" s="7" t="inlineStr">
+      <c r="M22" s="22" t="n"/>
+      <c r="N22" s="22" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
+      <c r="O22" s="21" t="n"/>
     </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>San Rafael, Dirty Devil</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>DS6624</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>Archery</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>Nov 11 2026 - Dec 17 2026</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr"/>
-      <c r="L23" s="7" t="n">
+      <c r="K23" s="23" t="n">
         <v>2025</v>
       </c>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="L23" s="24" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="N23" s="7" t="inlineStr"/>
-      <c r="O23" s="7" t="inlineStr">
+      <c r="M23" s="24" t="n"/>
+      <c r="N23" s="24" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
       </c>
+      <c r="O23" s="23" t="n"/>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>Mineral Mtns</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>DS6625</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K24" s="6" t="inlineStr"/>
-      <c r="L24" s="7" t="n">
+      <c r="K24" s="21" t="n">
         <v>2025</v>
       </c>
-      <c r="M24" s="7" t="inlineStr">
+      <c r="L24" s="22" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N24" s="7" t="inlineStr"/>
-      <c r="O24" s="7" t="inlineStr">
+      <c r="M24" s="22" t="n"/>
+      <c r="N24" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
+      <c r="O24" s="21" t="n"/>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>Escalante, East</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>DS6626</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J25" s="6" t="inlineStr">
+      <c r="J25" s="24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K25" s="6" t="inlineStr"/>
-      <c r="L25" s="7" t="n">
+      <c r="K25" s="23" t="n">
         <v>2025</v>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="L25" s="24" t="inlineStr">
         <is>
           <t>71.4</t>
         </is>
       </c>
-      <c r="N25" s="7" t="inlineStr"/>
-      <c r="O25" s="7" t="inlineStr">
+      <c r="M25" s="24" t="n"/>
+      <c r="N25" s="24" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
       </c>
+      <c r="O25" s="23" t="n"/>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>Escalante, West</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>DS6627</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>Male Only</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K26" s="6" t="inlineStr"/>
-      <c r="L26" s="7" t="n">
+      <c r="K26" s="21" t="n">
         <v>2025</v>
       </c>
-      <c r="M26" s="7" t="inlineStr">
+      <c r="L26" s="22" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N26" s="7" t="inlineStr"/>
-      <c r="O26" s="7" t="inlineStr">
+      <c r="M26" s="22" t="n"/>
+      <c r="N26" s="22" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
+      <c r="O26" s="21" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O26"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
-  <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="1" scale="35" fitToHeight="1" fitToWidth="1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
